--- a/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_M6B2-3_IN_Piura.xlsx
+++ b/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_M6B2-3_IN_Piura.xlsx
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C10" s="19">
         <f>ROUND(B10/$B$15*100,2)</f>
-        <v/>
+        <v>0.23</v>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="C11" s="21">
         <f>ROUND(B11/$B$15*100,2)</f>
-        <v/>
+        <v>9.27</v>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="C12" s="31">
         <f>ROUND(B12/$B$15*100,2)</f>
-        <v/>
+        <v>54.13</v>
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="C13" s="21">
         <f>ROUND(B13/$B$15*100,2)</f>
-        <v/>
+        <v>33.45</v>
       </c>
       <c r="D13" s="13" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="C14" s="19">
         <f>ROUND(B14/$B$15*100,2)</f>
-        <v/>
+        <v>2.91</v>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
@@ -1925,11 +1925,11 @@
       </c>
       <c r="B15" s="45">
         <f>SUM(B10:B14)</f>
-        <v/>
+        <v>160.9785</v>
       </c>
       <c r="C15" s="46">
         <f>SUM(C10:C14)</f>
-        <v/>
+        <v>99.99</v>
       </c>
       <c r="D15" s="44" t="inlineStr">
         <is>
@@ -1950,11 +1950,11 @@
       </c>
       <c r="B16" s="48">
         <f>SUM(B10:B11)</f>
-        <v/>
+        <v>15.3043</v>
       </c>
       <c r="C16" s="49">
         <f>ROUND(B16/B15*100,2)</f>
-        <v/>
+        <v>9.51</v>
       </c>
       <c r="D16" s="47" t="inlineStr">
         <is>
@@ -1975,11 +1975,11 @@
       </c>
       <c r="B17" s="48">
         <f>SUM(B12:B14)</f>
-        <v/>
+        <v>145.6742</v>
       </c>
       <c r="C17" s="49">
         <f>ROUND(B17/B15*100,2)</f>
-        <v/>
+        <v>90.49</v>
       </c>
       <c r="D17" s="47" t="inlineStr">
         <is>
@@ -2173,11 +2173,11 @@
       </c>
       <c r="B29" s="22">
         <f>SUM(B25:B28)</f>
-        <v/>
+        <v>161.0578</v>
       </c>
       <c r="C29" s="23">
         <f>SUM(C25:C28)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D29" s="17" t="inlineStr"/>
       <c r="E29" s="17" t="inlineStr"/>
@@ -2296,6 +2296,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
@@ -2442,6 +2443,7 @@
       <c r="F13" s="17" t="inlineStr"/>
       <c r="G13" s="17" t="inlineStr"/>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
@@ -2486,6 +2488,7 @@
       <c r="G16" s="8" t="n"/>
       <c r="H16" s="8" t="n"/>
     </row>
+    <row r="17"/>
     <row r="18" ht="144" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
@@ -2804,11 +2807,11 @@
       </c>
       <c r="B15" s="33">
         <f>SUM(B10:B14)</f>
-        <v/>
+        <v>1553.97</v>
       </c>
       <c r="C15" s="23">
         <f>SUM(C10:C14)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D15" s="17" t="inlineStr">
         <is>
@@ -2818,19 +2821,19 @@
       <c r="E15" s="17" t="inlineStr"/>
       <c r="F15" s="17">
         <f>ROUND(AVERAGE(F10:F14),2)</f>
-        <v/>
+        <v>18.02</v>
       </c>
       <c r="G15" s="22">
         <f>ROUND(AVERAGE(G10:G14),4)</f>
-        <v/>
+        <v>0.3393</v>
       </c>
       <c r="H15" s="23">
         <f>ROUND(AVERAGE(H10:H14),2)</f>
-        <v/>
+        <v>2.45</v>
       </c>
       <c r="I15" s="23">
         <f>ROUND(AVERAGE(I10:I14),2)</f>
-        <v/>
+        <v>97.63</v>
       </c>
     </row>
     <row r="16"/>
